--- a/Notes/notes-BlocksInUse.xlsx
+++ b/Notes/notes-BlocksInUse.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cygwin64\home\scrawford\silvermirror-local\Notes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A1F150D-90A9-4942-B8DD-86374F88F783}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E76B9E73-100B-4FE1-8433-40FF971BE931}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="42555" yWindow="-1035" windowWidth="14790" windowHeight="15585" activeTab="1" xr2:uid="{DCD1971C-D053-4CAC-94D5-99CE0AE4B60A}"/>
+    <workbookView xWindow="43095" yWindow="-1035" windowWidth="14610" windowHeight="15585" firstSheet="3" activeTab="4" xr2:uid="{DCD1971C-D053-4CAC-94D5-99CE0AE4B60A}"/>
   </bookViews>
   <sheets>
     <sheet name="TEMPLATE" sheetId="7" r:id="rId1"/>
@@ -6141,7 +6141,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="cellIs" dxfId="5" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8485,7 +8485,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10284,7 +10284,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12242,7 +12242,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14349,7 +14349,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17467,7 +17467,7 @@
         <v>129</v>
       </c>
       <c r="B130">
-        <f t="shared" ref="B130:B193" si="3">SUM(C130:ZZ130)/(A130)</f>
+        <f t="shared" ref="B130:B175" si="3">SUM(C130:ZZ130)/(A130)</f>
         <v>0</v>
       </c>
     </row>
@@ -17882,20 +17882,20 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D20:D22 D24:D1048576 D1">
-    <cfRule type="duplicateValues" dxfId="115" priority="5"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="D1 D20:D22 D24:D1048576">
-    <cfRule type="duplicateValues" dxfId="114" priority="4877"/>
+    <cfRule type="duplicateValues" dxfId="115" priority="4877"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4 D6:D11 D13:D14 D16 D18 D23">
-    <cfRule type="duplicateValues" dxfId="113" priority="4880"/>
+    <cfRule type="duplicateValues" dxfId="114" priority="4880"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D20:D22 D24:D1048576 D1">
+    <cfRule type="duplicateValues" dxfId="113" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E28 E36 E2 E4 E7 E9:E10 E13:E14 E18">
     <cfRule type="duplicateValues" dxfId="112" priority="4929"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F4 F12 F19 F28 F33 F38:F41">
-    <cfRule type="duplicateValues" dxfId="0" priority="4964"/>
+    <cfRule type="duplicateValues" dxfId="111" priority="4964"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -19571,15 +19571,15 @@
     <sortCondition ref="D1:D175"/>
   </sortState>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="cellIs" dxfId="111" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="110" priority="3" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:D2 D16:D22 D35 D37 D46 D49 D52:D53 D55:D1048576 D43 D41 D30:D32">
-    <cfRule type="duplicateValues" dxfId="110" priority="4844"/>
+    <cfRule type="duplicateValues" dxfId="109" priority="4844"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D55:D56 D58:D1048576 D52 D49 D20 D1">
-    <cfRule type="duplicateValues" dxfId="109" priority="4843"/>
+    <cfRule type="duplicateValues" dxfId="108" priority="4843"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -25648,237 +25648,237 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="cellIs" dxfId="108" priority="77" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="107" priority="77" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E37:E39 E60 E71 E88 E51 E63:E64 E75 F82:F83 E80:E81 F109 F118 F138 E137 F135:F136 E7 E3:E4">
-    <cfRule type="duplicateValues" dxfId="107" priority="308"/>
+    <cfRule type="duplicateValues" dxfId="106" priority="308"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F37:F38 F41:F46 F48 F60:F61 F63:F67 F87:F88 F110:F111 F117 F2 F8 F11:F12">
-    <cfRule type="duplicateValues" dxfId="106" priority="341"/>
+    <cfRule type="duplicateValues" dxfId="105" priority="341"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G7:G9 G11:G12 G21 G27 G32:G34 G37:G38 G41:G45 G48 G50 G60 G63:G64 G79 G82 G88:G93 G98:G99 G104 G108 G111:G112 G115 G117 G125">
-    <cfRule type="duplicateValues" dxfId="105" priority="462"/>
+    <cfRule type="duplicateValues" dxfId="104" priority="462"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G50 G60 G63:G64 G79 G82 G88:G93 G98:G99 G104 G108 G111:G112 G115 G117 G125">
-    <cfRule type="duplicateValues" dxfId="104" priority="449"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="449"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H169 H172 H2 H5 H8:H13 H15:H16 H28:H29 H31 H33:H34 H40:H41 H50 H61:H64 H78:H80 H82:H83 H86 H101 H110:H111 H120 H125 H127 H135:H137">
-    <cfRule type="duplicateValues" dxfId="103" priority="596"/>
+    <cfRule type="duplicateValues" dxfId="102" priority="596"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H169 H172 H41 H50 H61:H64 H78:H80 H82:H83 H86 H101 H110:H111 H120 H125 H127 H135:H137">
-    <cfRule type="duplicateValues" dxfId="102" priority="582"/>
+    <cfRule type="duplicateValues" dxfId="101" priority="582"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I8:I9 I11:I12 I16 I26 I30:I34 I48 I50 I56 I59:I60 I68 I79 I82:I83 I91:I93 I99 I101:I102 I107 I110:I111 I117 I125:I127">
-    <cfRule type="duplicateValues" dxfId="101" priority="654"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="654"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I82:I83 I91:I93 I99 I101:I102 I107 I110:I111 I117 I125:I127">
-    <cfRule type="duplicateValues" dxfId="100" priority="646"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="646"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J176 J2 J8:J9 J11:J12 J16 J24 J27 J33:J34 J48 J56 J78 J86 J90 J92:J93 J117 J125 J127 J135:J136">
-    <cfRule type="duplicateValues" dxfId="99" priority="681"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="681"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J176 J125 J127 J135:J136">
-    <cfRule type="duplicateValues" dxfId="98" priority="677"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="677"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K125 K127 K135:K136 K165 K176 K2 K9 K11:K12 K16 K23 K27 K33:K34 K36:K38 K40:K42 K44:K45 K50 K54 K56 K60 K63:K65 K69:K70 K73:K74 K78:K79 K82:K83 K88 K94 K98 K110:K111 K117 K120">
-    <cfRule type="duplicateValues" dxfId="97" priority="913"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="913"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K125 K127 K135:K136 K165 K176 K54 K56 K60 K63:K65 K69:K70 K73:K74 K78:K79 K82:K83 K88 K94 K98 K110:K111 K117 K120">
-    <cfRule type="duplicateValues" dxfId="96" priority="894"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="894"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L8:L9 L11:L12 L27 L37:L38 L41:L45 L48 L50 L54 L60 L63:L64 L77:L78 L80 L82:L83 L88 L100 L117">
-    <cfRule type="duplicateValues" dxfId="95" priority="950"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="950"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L77:L78 L80 L82:L83 L88 L100 L117">
-    <cfRule type="duplicateValues" dxfId="94" priority="944"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="944"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M41:M44 M48 M50 M54 M60 M64 M68 M78 M80 M86:M88 M98 M102 M113 M115 M120 M125 M2 M8 M11:M12 M33:M34">
-    <cfRule type="duplicateValues" dxfId="93" priority="998"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="998"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M86:M88 M98 M102 M113 M115 M120 M125">
-    <cfRule type="duplicateValues" dxfId="92" priority="991"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="991"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M126:M128 M124 M122 M117:M119 M114 M105:M106 M93 M85 M77 M63 M59 M56 M47 M45 M37:M38 M32 M27 M13:M15 M9 M7">
-    <cfRule type="duplicateValues" dxfId="91" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="59"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M126:M128 M124 M122 M117:M119 M114 M106">
-    <cfRule type="duplicateValues" dxfId="90" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="60"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N166 N168 N2 N7 N11:N12 N16 N24 N31:N32 N35:N40 N50 N56 N60 N63:N64 N68:N70 N73:N74 N77 N82:N83 N87 N94 N101 N110:N111 N127 N135:N136 N138">
-    <cfRule type="duplicateValues" dxfId="89" priority="1133"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="1133"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N166 N168 N64 N68:N70 N73:N74 N77 N82:N83 N87 N94 N101 N110:N111 N127 N135:N136 N138">
-    <cfRule type="duplicateValues" dxfId="88" priority="1119"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="1119"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="O88 O108:O109 O111 O120:O122 O124 O127 O129 O135:O137 O139 O141 O143:O147 O3:O4 O6 O11:O12 O16 O21:O23 O37:O38 O41:O42 O44:O45 O50 O52 O54:O56 O59 O68">
-    <cfRule type="duplicateValues" dxfId="87" priority="1272"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="1272"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="O88 O108:O109 O111 O120:O122 O124 O127 O129 O135:O137 O139 O141 O143:O147 O55:O56 O59 O68">
-    <cfRule type="duplicateValues" dxfId="86" priority="1257"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="1257"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P120:P121 P139 P142:P148 P6 P11 P16 P28 P30 P32 P47 P50 P53 P68 P78 P82 P86:P87 P109:P112">
-    <cfRule type="duplicateValues" dxfId="85" priority="1294"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="1294"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P120:P121 P139 P142:P148">
-    <cfRule type="duplicateValues" dxfId="84" priority="1290"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="1290"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q68 Q78 Q82 Q86 Q110:Q111 Q11:Q12 Q16 Q20 Q32 Q54">
-    <cfRule type="duplicateValues" dxfId="83" priority="1303"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="1303"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R79 R81:R83 R86 R109 R112 R117 R127 R136 R50 R9 R11:R12 R16 R20 R23">
-    <cfRule type="duplicateValues" dxfId="82" priority="1316"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="1316"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="S110:S112 S120 S127 S135:S136 S79 S81:S82 S97 S99 S2:S4 S9 S11:S12 S16 S20 S23:S24 S30 S32 S50 S56">
-    <cfRule type="duplicateValues" dxfId="81" priority="1347"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="1347"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="S110:S112 S120 S127 S135:S136 S99">
-    <cfRule type="duplicateValues" dxfId="80" priority="1342"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="1342"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="T9 T12 T25:T27 T30:T32 T40 T50 T68 T78:T79 T82 T93:T95 T100:T102 T104 T107 T117 T120">
-    <cfRule type="duplicateValues" dxfId="79" priority="1377"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="1377"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="T101:T102 T104 T107 T117 T120">
-    <cfRule type="duplicateValues" dxfId="78" priority="1372"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="1372"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U173 U117 U120 U135:U136 U46 U50 U66 U68 U78:U83 U87 U99:U102 U108:U109 U2 U12 U16 U21 U23:U26 U28 U31:U32">
-    <cfRule type="duplicateValues" dxfId="77" priority="1433"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="1433"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U173 U117 U120 U135:U136 U81:U83 U87 U99:U102 U108:U109">
-    <cfRule type="duplicateValues" dxfId="76" priority="1425"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="1425"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="V125 V127 V135:V136 V139:V148 V150:V151 V170:V171 V27:V28 V37:V38 V41:V42 V45 V50 V68 V88 V9">
-    <cfRule type="duplicateValues" dxfId="75" priority="1452"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="1452"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="V142:V148 V150:V151 V170:V171">
-    <cfRule type="duplicateValues" dxfId="74" priority="1449"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="1449"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="W139:W148 W150:W152 W123 W2 W7 W9 W37:W38 W50 W60 W63:W64 W68">
-    <cfRule type="duplicateValues" dxfId="73" priority="1465"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="1465"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="W146:W148 W150:W152">
-    <cfRule type="duplicateValues" dxfId="72" priority="1462"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="1462"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="X99:X102 X117 X140:X147 X149:X151 X2 X11:X12 X16 X32 X46:X47 X68 X78:X79 X82">
-    <cfRule type="duplicateValues" dxfId="71" priority="1479"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="1479"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="X142:X147 X149:X151">
-    <cfRule type="duplicateValues" dxfId="70" priority="1476"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="1476"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y2 Y8:Y9 Y11:Y12 Y27 Y30:Y31 Y37:Y38 Y41:Y45 Y48 Y50 Y56 Y60 Y63:Y64 Y71 Y75 Y79 Y83:Y84 Y86 Y88 Y93 Y99 Y101:Y102 Y105:Y106 Y117 Y125:Y128 Y135:Y138">
-    <cfRule type="duplicateValues" dxfId="69" priority="1634"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="1634"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y60 Y63:Y64 Y71 Y75 Y79 Y83:Y84 Y86 Y88 Y93 Y99 Y101:Y102 Y105:Y106 Y117 Y125:Y128 Y135:Y138">
-    <cfRule type="duplicateValues" dxfId="68" priority="1619"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="1619"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z2 Z7 Z9 Z11:Z12 Z14 Z16 Z32:Z34 Z37:Z38 Z41:Z47 Z50 Z56 Z59:Z60 Z63:Z64 Z68 Z71 Z75 Z77 Z84 Z88 Z101:Z102 Z105:Z106 Z110:Z111 Z117 Z124 Z127:Z128 Z153:Z164">
-    <cfRule type="duplicateValues" dxfId="67" priority="1845"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="1845"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z47 Z50 Z56 Z59:Z60 Z63:Z64 Z68 Z71 Z75 Z77 Z84 Z88 Z101:Z102 Z105:Z106 Z110:Z111 Z117 Z124 Z127:Z128 Z153:Z164">
-    <cfRule type="duplicateValues" dxfId="66" priority="1827"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="1827"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA102 AA107 AA117 AA6 AA8 AA11:AA12 AA25:AA26 AA30 AA32 AA37 AA41:AA42 AA44:AA45 AA47:AA48 AA50 AA63:AA64 AA68 AA79 AA88:AA92">
-    <cfRule type="duplicateValues" dxfId="65" priority="1882"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="1882"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA102 AA107 AA117 AA68 AA79 AA88:AA92">
-    <cfRule type="duplicateValues" dxfId="64" priority="1876"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="1876"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB6 AB8 AB11:AB13 AB15 AB30:AB32 AB37:AB38 AB42 AB44:AB45 AB47 AB50 AB60:AB62 AB68 AB77:AB78 AB80 AB82:AB83 AB86:AB88 AB97 AB101:AB102 AB109:AB112 AB117 AB120">
-    <cfRule type="duplicateValues" dxfId="63" priority="1974"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="1974"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB62 AB68 AB77:AB78 AB80 AB82:AB83 AB86:AB88 AB97 AB101:AB102 AB109:AB112 AB117 AB120">
-    <cfRule type="duplicateValues" dxfId="62" priority="1963"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="1963"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC166 AC168 AC3:AC4 AC6 AC8:AC9 AC11:AC12 AC16 AC27 AC30:AC32 AC37:AC38 AC41:AC47 AC50 AC60 AC63 AC68 AC82 AC88 AC91 AC101:AC102 AC112 AC117 AC121 AC123 AC125 AC127 AC139:AC148">
-    <cfRule type="duplicateValues" dxfId="61" priority="2184"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="2184"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC166 AC168 AC45:AC47 AC50 AC60 AC63 AC68 AC82 AC88 AC91 AC101:AC102 AC112 AC117 AC121 AC123 AC125 AC127 AC139:AC148">
-    <cfRule type="duplicateValues" dxfId="60" priority="2166"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="2166"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD101:AD102 AD112 AD121 AD123 AD139:AD146 AD148 AD6:AD9 AD11:AD12 AD16 AD30:AD32 AD38 AD42 AD44:AD47 AD50 AD60 AD64 AD68 AD88">
-    <cfRule type="duplicateValues" dxfId="59" priority="2250"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="2250"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD101:AD102 AD112 AD121 AD123 AD139:AD146 AD148 AD64 AD68 AD88">
-    <cfRule type="duplicateValues" dxfId="58" priority="2241"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="2241"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE3:AE4 AE8:AE9 AE11:AE12 AE16 AE27 AE30:AE32 AE37:AE38 AE41:AE45 AE48 AE50 AE56 AE60 AE63:AE64 AE68 AE88 AE91 AE93 AE101:AE102 AE105 AE109 AE112 AE117 AE125:AE127 AE135:AE138">
-    <cfRule type="duplicateValues" dxfId="57" priority="2421"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="2421"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE48 AE50 AE56 AE60 AE63:AE64 AE68 AE88 AE91 AE93 AE101:AE102 AE105 AE109 AE112 AE117 AE125:AE127 AE135:AE138">
-    <cfRule type="duplicateValues" dxfId="56" priority="2405"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="2405"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF88:AF89 AF91:AF92 AF97 AF102 AF115 AF125 AF7:AF9 AF11:AF12 AF16 AF30:AF34 AF37 AF41:AF46 AF48 AF50 AF54 AF60 AF63:AF64">
-    <cfRule type="duplicateValues" dxfId="55" priority="2507"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="2507"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF88:AF89 AF91:AF92 AF97 AF102 AF115 AF125 AF48 AF50 AF54 AF60 AF63:AF64">
-    <cfRule type="duplicateValues" dxfId="54" priority="2496"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="2496"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG30:AG31 AG33:AG34 AG50 AG56:AG59 AG61:AG62 AG78:AG81 AG83 AG85 AG87 AG98 AG101:AG102 AG117 AG120 AG127 AG2 AG9 AG11:AG12">
-    <cfRule type="duplicateValues" dxfId="53" priority="2571"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="2571"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG81 AG83 AG85 AG87 AG98 AG101:AG102 AG117 AG120 AG127">
-    <cfRule type="duplicateValues" dxfId="52" priority="2562"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="2562"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH2:AH4 AH8:AH9 AH11 AH13:AH19 AH27:AH29 AH33:AH34 AH38 AH42 AH45 AH48:AH50 AH53 AH60 AH64 AH78:AH79 AH83 AH87:AH88 AH103 AH109 AH115:AH117 AH120 AH125 AH127">
-    <cfRule type="duplicateValues" dxfId="51" priority="2738"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="2738"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH38 AH42 AH45 AH48:AH50 AH53 AH60 AH64 AH78:AH79 AH83 AH87:AH88 AH103 AH109 AH115:AH117 AH120 AH125 AH127">
-    <cfRule type="duplicateValues" dxfId="50" priority="2722"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="2722"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI166 AI2:AI4 AI8:AI9 AI11 AI13:AI16 AI20 AI27:AI29 AI33:AI34 AI37 AI41:AI42 AI45 AI48 AI53 AI56 AI59:AI60 AI63:AI64 AI67 AI78 AI82:AI83 AI85 AI87:AI88 AI110:AI112 AI114:AI120 AI125:AI127">
-    <cfRule type="duplicateValues" dxfId="49" priority="2908"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="2908"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI166 AI42 AI45 AI48 AI53 AI56 AI59:AI60 AI63:AI64 AI67 AI78 AI82:AI83 AI85 AI87:AI88 AI110:AI112 AI114:AI120 AI125:AI127">
-    <cfRule type="duplicateValues" dxfId="48" priority="2892"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="2892"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ169 AJ2:AJ4 AJ6 AJ8 AJ10:AJ11 AJ13:AJ20 AJ22 AJ25:AJ28 AJ32:AJ34 AJ38 AJ40 AJ42 AJ44:AJ45 AJ48:AJ51 AJ55 AJ68 AJ78:AJ79 AJ81:AJ83 AJ86:AJ88 AJ93:AJ94 AJ96 AJ99 AJ101 AJ108:AJ111 AJ113 AJ115:AJ117 AJ125">
-    <cfRule type="duplicateValues" dxfId="47" priority="3182"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="3182"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ169 AJ27:AJ28 AJ32:AJ34 AJ38 AJ40 AJ42 AJ44:AJ45 AJ48:AJ51 AJ55 AJ68 AJ78:AJ79 AJ81:AJ83 AJ86:AJ88 AJ93:AJ94 AJ96 AJ99 AJ101 AJ108:AJ111 AJ113 AJ115:AJ117 AJ125">
-    <cfRule type="duplicateValues" dxfId="46" priority="3161"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="3161"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK108 AK115:AK116 AK120:AK121 AK125 AK127 AK174 AK2 AK6 AK9 AK13:AK20 AK22 AK25:AK26 AK28 AK30:AK34 AK37 AK46:AK47 AK50 AK54 AK56 AK63:AK64 AK68:AK70 AK73:AK74 AK87:AK88 AK101">
-    <cfRule type="duplicateValues" dxfId="45" priority="3369"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="3369"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK108 AK115:AK116 AK120:AK121 AK125 AK127 AK174 AK33:AK34 AK37 AK46:AK47 AK50 AK54 AK56 AK63:AK64 AK68:AK70 AK73:AK74 AK87:AK88 AK101">
-    <cfRule type="duplicateValues" dxfId="44" priority="3352"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="3352"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AL3:AL4 AL7 AL9 AL33:AL34 AL37:AL38 AL41 AL43 AL45 AL50 AL56 AL60 AL63:AL64 AL88 AL105:AL106 AL115 AL122 AL124:AL128">
-    <cfRule type="duplicateValues" dxfId="43" priority="3395"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="3395"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AL106 AL115 AL122 AL124:AL128">
-    <cfRule type="duplicateValues" dxfId="42" priority="3390"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="3390"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM97 AM104:AM107 AM109:AM112 AM115:AM117 AM120 AM122 AM125:AM128 AM131:AM134 AM2 AM4:AM6 AM8 AM10:AM11 AM13:AM19 AM25:AM26 AM32:AM34 AM48:AM49 AM54 AM56 AM59 AM68 AM78:AM79 AM85:AM87">
-    <cfRule type="duplicateValues" dxfId="41" priority="3566"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="3566"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM97 AM104:AM107 AM109:AM112 AM115:AM117 AM120 AM122 AM125:AM128 AM131:AM134 AM34 AM48:AM49 AM54 AM56 AM59 AM68 AM78:AM79 AM85:AM87">
-    <cfRule type="duplicateValues" dxfId="40" priority="3549"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="3549"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AN165 AN168:AN169 AN2:AN4 AN8:AN9 AN11:AN19 AN24 AN28 AN30:AN34 AN37:AN38 AN50 AN56:AN64 AN71 AN75 AN79 AN82:AN83 AN85:AN93 AN96 AN110:AN112 AN115:AN117 AN120 AN124:AN125 AN127 AN135:AN137">
-    <cfRule type="duplicateValues" dxfId="39" priority="3772"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="3772"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AN165 AN168:AN169 AN32:AN34 AN37:AN38 AN50 AN56:AN64 AN71 AN75 AN79 AN82:AN83 AN85:AN93 AN96 AN110:AN112 AN115:AN117 AN120 AN124:AN125 AN127 AN135:AN137">
-    <cfRule type="duplicateValues" dxfId="38" priority="3754"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="3754"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AO175:AO176 AO170 AO56:AO59 AO61:AO62 AO69:AO70 AO73:AO74 AO78:AO82 AO85:AO87 AO98:AO100 AO105:AO106 AO115:AO116 AO120 AO125 AO127:AO128 AO130 AO135:AO137 AO2 AO5 AO9 AO13:AO19 AO23:AO24 AO33:AO36 AO39:AO40">
-    <cfRule type="duplicateValues" dxfId="37" priority="3942"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="3942"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AO175:AO176 AO170 AO56:AO59 AO61:AO62 AO69:AO70 AO73:AO74 AO78:AO82 AO85:AO87 AO98:AO100 AO105:AO106 AO115:AO116 AO120 AO125 AO127:AO128 AO130 AO135:AO137">
-    <cfRule type="duplicateValues" dxfId="36" priority="3926"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="3926"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AP171 AP103 AP115:AP116 AP124:AP125 AP127 AP139 AP143:AP148 AP150:AP152 AP2 AP6 AP9 AP13:AP15 AP17:AP19 AP33:AP34 AP50 AP56 AP59 AP68">
-    <cfRule type="duplicateValues" dxfId="35" priority="3982"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="3982"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AP171 AP124:AP125 AP127 AP139 AP143:AP148 AP150:AP152">
-    <cfRule type="duplicateValues" dxfId="34" priority="3976"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="3976"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AQ99:AQ100 AQ111 AQ117 AQ122 AQ124 AQ3:AQ4 AQ7:AQ8 AQ11 AQ37:AQ38 AQ41:AQ45 AQ48 AQ60 AQ63:AQ64 AQ66 AQ78:AQ83 AQ88">
-    <cfRule type="duplicateValues" dxfId="33" priority="4025"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="4025"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AQ99:AQ100 AQ111 AQ117 AQ122 AQ124 AQ79:AQ83 AQ88">
-    <cfRule type="duplicateValues" dxfId="32" priority="4018"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="4018"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -27377,7 +27377,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="16">
         <v>64</v>
       </c>
@@ -27389,7 +27389,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="16">
         <v>65</v>
       </c>
@@ -27401,7 +27401,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="16">
         <v>66</v>
       </c>
@@ -27413,7 +27413,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="16">
         <v>67</v>
       </c>
@@ -27425,7 +27425,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="16">
         <v>68</v>
       </c>
@@ -27437,7 +27437,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="16">
         <v>69</v>
       </c>
@@ -27449,7 +27449,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="16">
         <v>70</v>
       </c>
@@ -27461,7 +27461,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="16">
         <v>71</v>
       </c>
@@ -27473,7 +27473,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="16">
         <v>72</v>
       </c>
@@ -27485,16 +27485,19 @@
         <v>72</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="16">
         <v>73</v>
       </c>
       <c r="B74">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="H74" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="16">
         <v>74</v>
       </c>
@@ -27506,7 +27509,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="16">
         <v>75</v>
       </c>
@@ -27518,7 +27521,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="16">
         <v>76</v>
       </c>
@@ -27530,7 +27533,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="16">
         <v>77</v>
       </c>
@@ -27542,7 +27545,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="16">
         <v>78</v>
       </c>
@@ -27554,7 +27557,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="16">
         <v>79</v>
       </c>
@@ -28431,66 +28434,66 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="cellIs" dxfId="31" priority="20" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="30" priority="20" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1 D85:D1048576 D80">
-    <cfRule type="duplicateValues" dxfId="30" priority="4204"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="4204"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D3 D5:D11 D13:D15 D17:D19 D25:D37 D41:D44 D46:D50 D57:D61 D66 D69:D71 D73 D75 D81:D84">
-    <cfRule type="duplicateValues" dxfId="29" priority="4216"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="4216"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D29:D37 D41:D44 D46:D50 D57:D61 D66 D69:D71 D73 D75 D81:D84">
-    <cfRule type="duplicateValues" dxfId="28" priority="4207"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="4207"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D85:D1048576 D80 D1">
-    <cfRule type="duplicateValues" dxfId="27" priority="4206"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="4206"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3 E6:E7 E9:E11 E13:E14 E17:E18 E27:E28 E32:E34 E37 E41:E42 E44">
-    <cfRule type="duplicateValues" dxfId="26" priority="4279"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="4279"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E44">
-    <cfRule type="duplicateValues" dxfId="25" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3 F5:F7 F9:F15 F17:F19 F25:F26 F29:F32 F35:F37 F41:F42 F44 F49 F64">
-    <cfRule type="duplicateValues" dxfId="24" priority="4372"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="4372"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F31:F32 F35:F37 F41:F42 F44 F49 F64">
-    <cfRule type="duplicateValues" dxfId="23" priority="4366"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="4366"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3 H5:H7 H9:H11 H13:H18 H30 H36:H38 H40 H45:H48">
-    <cfRule type="duplicateValues" dxfId="22" priority="4421"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="4421"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H45:H48">
-    <cfRule type="duplicateValues" dxfId="21" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I61:I63 I3 I5:I7 I9:I11 I13:I19 I21:I22 I26:I33 I36:I44 I50 I55">
-    <cfRule type="duplicateValues" dxfId="20" priority="4499"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="4499"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I61:I63 I28:I33 I36:I44 I50 I55">
-    <cfRule type="duplicateValues" dxfId="19" priority="4494"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="4494"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J3 J5:J7 J9:J11 J13:J19 J28 J30:J31 J33:J34 J38 J40 J42 J55">
-    <cfRule type="duplicateValues" dxfId="18" priority="4586"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="4586"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J34 J38 J40 J42 J55">
-    <cfRule type="duplicateValues" dxfId="17" priority="4581"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="4581"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K3 K5:K7 K9:K11 K13:K15 K17:K18 K26 K28:K30 K34 K41 K43:K44 K49:K50">
-    <cfRule type="duplicateValues" dxfId="16" priority="4658"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="4658"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K43:K44 K49:K50">
-    <cfRule type="duplicateValues" dxfId="15" priority="4656"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="4656"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L3 L6 L9:L11 L14 L17:L18 L25 L28 L31:L32 L36:L37 L42:L43">
-    <cfRule type="duplicateValues" dxfId="14" priority="4721"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="4721"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M89:M96 M3 M5:M7 M9:M11 M13:M19 M30:M31 M36:M38 M41:M48 M55:M56 M58">
-    <cfRule type="duplicateValues" dxfId="13" priority="4795"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="4795"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M89:M96 M38 M41:M48 M55:M56 M58">
-    <cfRule type="duplicateValues" dxfId="12" priority="4805"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="4805"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -30595,15 +30598,15 @@
     <sortCondition ref="M1:M176"/>
   </sortState>
   <conditionalFormatting sqref="B1:C1048576">
-    <cfRule type="cellIs" dxfId="11" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="10" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M8:M11">
-    <cfRule type="duplicateValues" dxfId="10" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M27:M61">
-    <cfRule type="duplicateValues" dxfId="9" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="7"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -32442,7 +32445,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="cellIs" dxfId="8" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -34411,7 +34414,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="cellIs" dxfId="7" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="6" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -36221,7 +36224,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="cellIs" dxfId="6" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Notes/notes-BlocksInUse.xlsx
+++ b/Notes/notes-BlocksInUse.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cygwin64\home\scrawford\silvermirror-local\Notes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E76B9E73-100B-4FE1-8433-40FF971BE931}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48E0B543-8E76-47EE-BB53-DB0EC42AD63C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43095" yWindow="-1035" windowWidth="14610" windowHeight="15585" firstSheet="3" activeTab="4" xr2:uid="{DCD1971C-D053-4CAC-94D5-99CE0AE4B60A}"/>
+    <workbookView xWindow="43095" yWindow="-1035" windowWidth="14610" windowHeight="15585" firstSheet="3" activeTab="3" xr2:uid="{DCD1971C-D053-4CAC-94D5-99CE0AE4B60A}"/>
   </bookViews>
   <sheets>
     <sheet name="TEMPLATE" sheetId="7" r:id="rId1"/>
@@ -25511,7 +25511,10 @@
       </c>
       <c r="B167" s="46">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O167" s="17">
+        <v>166</v>
       </c>
     </row>
     <row r="168" spans="1:42" x14ac:dyDescent="0.25">

--- a/Notes/notes-BlocksInUse.xlsx
+++ b/Notes/notes-BlocksInUse.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cygwin64\home\scrawford\silvermirror-local\Notes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27EF5279-461C-47A2-8A68-3A1892EB9A27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECA99B72-C8F5-42B5-BBA0-A888AC341357}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12690" yWindow="0" windowWidth="16215" windowHeight="15585" activeTab="1" xr2:uid="{DCD1971C-D053-4CAC-94D5-99CE0AE4B60A}"/>
+    <workbookView xWindow="900" yWindow="585" windowWidth="25215" windowHeight="14775" activeTab="2" xr2:uid="{DCD1971C-D053-4CAC-94D5-99CE0AE4B60A}"/>
   </bookViews>
   <sheets>
     <sheet name="TEMPLATE" sheetId="7" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="254">
   <si>
     <t>Celadon Game Corner</t>
   </si>
@@ -817,6 +817,9 @@
   <si>
     <t>Indigo Plateau Pokecenter 1F</t>
   </si>
+  <si>
+    <t>Celadon Hotel      (tile swap)</t>
+  </si>
 </sst>
 </file>
 
@@ -1066,7 +1069,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1256,10 +1259,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -27423,7 +27422,7 @@
     <col min="3" max="3" width="1.7109375" style="1" customWidth="1"/>
     <col min="4" max="4" width="10.7109375" style="72"/>
     <col min="5" max="5" width="10.7109375" style="14"/>
-    <col min="6" max="6" width="10.7109375" style="86"/>
+    <col min="6" max="6" width="10.7109375" style="1"/>
     <col min="7" max="7" width="10.7109375" style="14"/>
     <col min="8" max="8" width="10.7109375" style="1"/>
     <col min="9" max="9" width="10.7109375" style="14"/>
@@ -27459,11 +27458,14 @@
       <c r="E1" s="12" t="s">
         <v>250</v>
       </c>
-      <c r="F1" s="85" t="s">
+      <c r="F1" s="8" t="s">
         <v>251</v>
       </c>
       <c r="G1" s="12" t="s">
         <v>252</v>
+      </c>
+      <c r="H1" s="67" t="s">
+        <v>253</v>
       </c>
       <c r="I1" s="12"/>
       <c r="K1" s="12"/>
@@ -27529,9 +27531,15 @@
       </c>
       <c r="B5">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="D5" s="72">
+        <v>4</v>
       </c>
       <c r="G5" s="14">
+        <v>4</v>
+      </c>
+      <c r="H5" s="1">
         <v>4</v>
       </c>
     </row>
@@ -27541,12 +27549,15 @@
       </c>
       <c r="B6">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" s="72">
         <v>5</v>
       </c>
       <c r="G6" s="14">
+        <v>5</v>
+      </c>
+      <c r="H6" s="1">
         <v>5</v>
       </c>
     </row>
@@ -27601,9 +27612,12 @@
       </c>
       <c r="B10">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" s="72">
+        <v>9</v>
+      </c>
+      <c r="H10" s="1">
         <v>9</v>
       </c>
     </row>
@@ -27628,12 +27642,15 @@
       </c>
       <c r="B12">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" s="72">
         <v>11</v>
       </c>
       <c r="G12" s="14">
+        <v>11</v>
+      </c>
+      <c r="H12" s="1">
         <v>11</v>
       </c>
     </row>
@@ -27840,7 +27857,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F29" s="86">
+      <c r="F29" s="1">
         <v>28</v>
       </c>
     </row>
@@ -27888,7 +27905,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F33" s="86">
+      <c r="F33" s="1">
         <v>32</v>
       </c>
     </row>
@@ -27924,7 +27941,7 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="F36" s="86">
+      <c r="F36" s="1">
         <v>35</v>
       </c>
       <c r="G36" s="14">
@@ -27951,7 +27968,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="F38" s="86">
+      <c r="F38" s="1">
         <v>37</v>
       </c>
     </row>
@@ -27963,7 +27980,7 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="F39" s="86">
+      <c r="F39" s="1">
         <v>38</v>
       </c>
       <c r="G39" s="14">
@@ -27978,7 +27995,7 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="F40" s="86">
+      <c r="F40" s="1">
         <v>39</v>
       </c>
       <c r="G40" s="14">
@@ -28029,7 +28046,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="F44" s="86">
+      <c r="F44" s="1">
         <v>43</v>
       </c>
     </row>
@@ -28041,7 +28058,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="F45" s="86">
+      <c r="F45" s="1">
         <v>44</v>
       </c>
     </row>
@@ -28053,7 +28070,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="F46" s="86">
+      <c r="F46" s="1">
         <v>45</v>
       </c>
     </row>
@@ -28065,7 +28082,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="F47" s="86">
+      <c r="F47" s="1">
         <v>46</v>
       </c>
     </row>
@@ -28077,7 +28094,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="F48" s="86">
+      <c r="F48" s="1">
         <v>47</v>
       </c>
     </row>
@@ -28089,7 +28106,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="F49" s="86">
+      <c r="F49" s="1">
         <v>48</v>
       </c>
     </row>
@@ -28101,7 +28118,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="F50" s="86">
+      <c r="F50" s="1">
         <v>49</v>
       </c>
     </row>
@@ -29439,7 +29456,7 @@
         <v>193</v>
       </c>
       <c r="B194">
-        <f t="shared" ref="B194:B257" si="4">SUM(C194:ZZ194)/(A194)</f>
+        <f t="shared" ref="B194:B255" si="4">SUM(C194:ZZ194)/(A194)</f>
         <v>0</v>
       </c>
     </row>
@@ -37535,10 +37552,7 @@
       </c>
       <c r="B44">
         <f t="shared" si="1"/>
-        <v>2.3255813953488372E-2</v>
-      </c>
-      <c r="C44" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:35" x14ac:dyDescent="0.25">
@@ -40436,7 +40450,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A145" s="13">
         <v>144</v>
       </c>
@@ -40445,7 +40459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A146" s="13">
         <v>145</v>
       </c>
@@ -40454,7 +40468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A147" s="13">
         <v>146</v>
       </c>
@@ -40466,7 +40480,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A148" s="13">
         <v>147</v>
       </c>
@@ -40478,7 +40492,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A149" s="13">
         <v>148</v>
       </c>
@@ -40487,7 +40501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A150" s="13">
         <v>149</v>
       </c>
@@ -40496,7 +40510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A151" s="13">
         <v>150</v>
       </c>
@@ -40505,70 +40519,91 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A152" s="13">
         <v>151</v>
       </c>
       <c r="B152">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T152" s="1">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="153" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A153" s="13">
         <v>152</v>
       </c>
       <c r="B153">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T153" s="1">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="154" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A154" s="13">
         <v>153</v>
       </c>
       <c r="B154">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T154" s="1">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="155" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A155" s="13">
         <v>154</v>
       </c>
       <c r="B155">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="156" spans="1:14" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T155" s="1">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="156" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A156" s="13">
         <v>155</v>
       </c>
       <c r="B156">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T156" s="1">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="157" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A157" s="13">
         <v>156</v>
       </c>
       <c r="B157">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="158" spans="1:14" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T157" s="1">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="158" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A158" s="13">
         <v>157</v>
       </c>
       <c r="B158">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="159" spans="1:14" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="T158" s="1">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="159" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A159" s="13">
         <v>158</v>
       </c>
@@ -40577,13 +40612,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A160" s="13">
         <v>159</v>
       </c>
       <c r="B160">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T160" s="1">
+        <v>159</v>
       </c>
     </row>
     <row r="161" spans="1:28" x14ac:dyDescent="0.25">
@@ -40682,7 +40720,10 @@
       </c>
       <c r="B171">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AA171" s="14">
+        <v>170</v>
       </c>
     </row>
     <row r="172" spans="1:28" x14ac:dyDescent="0.25">

--- a/Notes/notes-BlocksInUse.xlsx
+++ b/Notes/notes-BlocksInUse.xlsx
@@ -2335,7 +2335,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="cellIs" dxfId="29" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="27" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
